--- a/Unity/Assets/Config/Excel/EquipConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EquipConfig.xlsx
@@ -1,38 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\《梦境之旅》Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F688D8BD-81A3-4762-A226-D202D90B48A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="E3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -41,7 +47,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -51,7 +56,6 @@
           <rPr>
             <sz val="10"/>
             <rFont val="微软雅黑"/>
-            <family val="2"/>
             <charset val="134"/>
           </rPr>
           <t>1. 暴击、连击、反击、吸血、闪避
@@ -59,14 +63,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="G3" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>admin:</t>
@@ -75,7 +78,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -85,7 +87,6 @@
           <rPr>
             <sz val="10"/>
             <rFont val="微软雅黑"/>
-            <family val="2"/>
             <charset val="134"/>
           </rPr>
           <t>1. 表示金币
@@ -98,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="67">
   <si>
     <t>Id</t>
   </si>
@@ -142,6 +143,9 @@
     <t>最高攻速</t>
   </si>
   <si>
+    <t>最低移速</t>
+  </si>
+  <si>
     <t>暴击</t>
   </si>
   <si>
@@ -172,6 +176,81 @@
     <t>抗闪避</t>
   </si>
   <si>
+    <t>ItemName</t>
+  </si>
+  <si>
+    <t>HideType</t>
+  </si>
+  <si>
+    <t>HideShowPro</t>
+  </si>
+  <si>
+    <t>SellResourcesType</t>
+  </si>
+  <si>
+    <t>SellResourcesValue</t>
+  </si>
+  <si>
+    <t>Equip_MinAct</t>
+  </si>
+  <si>
+    <t>Equip_MaxAct</t>
+  </si>
+  <si>
+    <t>Equip_MinDef</t>
+  </si>
+  <si>
+    <t>Equip_MaxAdf</t>
+  </si>
+  <si>
+    <t>Equip_MinHp</t>
+  </si>
+  <si>
+    <t>Equip_MaxHp</t>
+  </si>
+  <si>
+    <t>Equip_MinAtkSpeed</t>
+  </si>
+  <si>
+    <t>Equip_MaxAtkSpeed</t>
+  </si>
+  <si>
+    <t>Equip_MinMoveSpeed</t>
+  </si>
+  <si>
+    <t>Equip_MaxMoveSpeed</t>
+  </si>
+  <si>
+    <t>Equip_Cri</t>
+  </si>
+  <si>
+    <t>Equip_Combo</t>
+  </si>
+  <si>
+    <t>Equip_Counterattack</t>
+  </si>
+  <si>
+    <t>Equip_LifeSteal</t>
+  </si>
+  <si>
+    <t>Equip_Eva</t>
+  </si>
+  <si>
+    <t>Equip_ReCri</t>
+  </si>
+  <si>
+    <t>Equip_ReCombo</t>
+  </si>
+  <si>
+    <t>Equip_ReCounterattack</t>
+  </si>
+  <si>
+    <t>Equip_ReLifeSteal</t>
+  </si>
+  <si>
+    <t>Equip_ReEva</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -217,128 +296,23 @@
     <t>一个项链</t>
   </si>
   <si>
-    <t>一个护符</t>
-  </si>
-  <si>
     <t>一个饰品</t>
   </si>
   <si>
     <t>一个武器</t>
-  </si>
-  <si>
-    <t>Id</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemName</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>HideType</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>HideShowPro</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equip_MinAct</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equip_MaxAct</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equip_MinDef</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equip_MaxAdf</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equip_MinHp</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equip_MaxHp</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equip_MinAtkSpeed</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equip_MaxAtkSpeed</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>最低移速</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equip_MinMoveSpeed</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equip_MaxMoveSpeed</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equip_Cri</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equip_Combo</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equip_Counterattack</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equip_LifeSteal</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equip_Eva</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equip_ReCri</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equip_ReCombo</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equip_ReCounterattack</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equip_ReLifeSteal</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equip_ReEva</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>SellResourcesType</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>SellResourcesValue</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -350,44 +324,176 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="9"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -406,8 +512,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -458,9 +750,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -490,17 +1024,61 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -758,20 +1336,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:AB74"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A3:AB73"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.875" style="4" customWidth="1"/>
     <col min="3" max="16384" width="17.875" style="4"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:28" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="5" t="s">
@@ -817,224 +1395,224 @@
         <v>13</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="R3" s="6" t="s">
         <v>13</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U3" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V3" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W3" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X3" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z3" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA3" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB3" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q4" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="R4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="S4" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="U4" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="V4" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="W4" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="X4" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="I4" s="7" t="s">
+      <c r="Y4" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="Z4" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="AA4" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="AB4" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="M4" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="P4" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q4" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="R4" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="S4" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="T4" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="U4" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="V4" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="W4" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="X4" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y4" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="Z4" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA4" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="AB4" s="7" t="s">
-        <v>66</v>
-      </c>
     </row>
-    <row r="5" spans="1:28" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" s="2" customFormat="1" customHeight="1" spans="1:28">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="5" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="R5" s="5" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="S5" s="5" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="T5" s="5" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="U5" s="5" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="V5" s="5" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="W5" s="5" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="X5" s="5" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="Y5" s="5" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="Z5" s="5" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="AA5" s="5" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="AB5" s="5" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" s="3" customFormat="1" customHeight="1" spans="3:28">
       <c r="C6" s="3">
         <v>12000001</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="F6" s="3">
         <v>0.02</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="I6" s="3">
         <v>20</v>
@@ -1088,33 +1666,33 @@
         <v>0.06</v>
       </c>
       <c r="Z6" s="3">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="AA6" s="3">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="AB6" s="3">
         <v>0.08</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" s="3" customFormat="1" customHeight="1" spans="3:28">
       <c r="C7" s="3">
         <v>12000002</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="F7" s="3">
         <v>0.02</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="I7" s="3">
         <v>20</v>
@@ -1168,33 +1746,33 @@
         <v>0.06</v>
       </c>
       <c r="Z7" s="3">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="AA7" s="3">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="AB7" s="3">
         <v>0.08</v>
       </c>
     </row>
-    <row r="8" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" s="3" customFormat="1" customHeight="1" spans="3:28">
       <c r="C8" s="3">
         <v>12000003</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="F8" s="3">
         <v>0.02</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="I8" s="3">
         <v>20</v>
@@ -1248,33 +1826,33 @@
         <v>0.06</v>
       </c>
       <c r="Z8" s="3">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="AA8" s="3">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="AB8" s="3">
         <v>0.08</v>
       </c>
     </row>
-    <row r="9" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" s="3" customFormat="1" customHeight="1" spans="3:28">
       <c r="C9" s="3">
         <v>12000004</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="F9" s="3">
         <v>0.02</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="I9" s="3">
         <v>20</v>
@@ -1328,33 +1906,33 @@
         <v>0.06</v>
       </c>
       <c r="Z9" s="3">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="AA9" s="3">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="AB9" s="3">
         <v>0.08</v>
       </c>
     </row>
-    <row r="10" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" s="3" customFormat="1" customHeight="1" spans="3:28">
       <c r="C10" s="3">
         <v>12000005</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="F10" s="3">
         <v>0.02</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="I10" s="3">
         <v>20</v>
@@ -1408,33 +1986,33 @@
         <v>0.06</v>
       </c>
       <c r="Z10" s="3">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="AA10" s="3">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="AB10" s="3">
         <v>0.08</v>
       </c>
     </row>
-    <row r="11" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" s="3" customFormat="1" customHeight="1" spans="3:28">
       <c r="C11" s="3">
         <v>12000006</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="F11" s="3">
         <v>0.02</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="I11" s="3">
         <v>20</v>
@@ -1488,33 +2066,33 @@
         <v>0.06</v>
       </c>
       <c r="Z11" s="3">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="AA11" s="3">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="AB11" s="3">
         <v>0.08</v>
       </c>
     </row>
-    <row r="12" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" s="3" customFormat="1" customHeight="1" spans="3:28">
       <c r="C12" s="3">
         <v>12000007</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="F12" s="3">
         <v>0.02</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="I12" s="3">
         <v>20</v>
@@ -1568,33 +2146,33 @@
         <v>0.06</v>
       </c>
       <c r="Z12" s="3">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="AA12" s="3">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="AB12" s="3">
         <v>0.08</v>
       </c>
     </row>
-    <row r="13" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" s="3" customFormat="1" customHeight="1" spans="3:28">
       <c r="C13" s="3">
         <v>12000008</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="F13" s="3">
         <v>0.02</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="I13" s="3">
         <v>20</v>
@@ -1648,33 +2226,33 @@
         <v>0.06</v>
       </c>
       <c r="Z13" s="3">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="AA13" s="3">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="AB13" s="3">
         <v>0.08</v>
       </c>
     </row>
-    <row r="14" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" s="3" customFormat="1" customHeight="1" spans="3:28">
       <c r="C14" s="3">
         <v>12000009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="F14" s="3">
         <v>0.02</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="I14" s="3">
         <v>20</v>
@@ -1728,33 +2306,33 @@
         <v>0.06</v>
       </c>
       <c r="Z14" s="3">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="AA14" s="3">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="AB14" s="3">
         <v>0.08</v>
       </c>
     </row>
-    <row r="15" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" s="3" customFormat="1" customHeight="1" spans="3:28">
       <c r="C15" s="3">
         <v>12000010</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="F15" s="3">
         <v>0.02</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="I15" s="3">
         <v>20</v>
@@ -1808,156 +2386,76 @@
         <v>0.06</v>
       </c>
       <c r="Z15" s="3">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="AA15" s="3">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07</v>
       </c>
       <c r="AB15" s="3">
         <v>0.08</v>
       </c>
     </row>
-    <row r="16" spans="1:28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C16" s="3">
-        <v>12000011</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="3">
-        <v>20</v>
-      </c>
-      <c r="J16" s="3">
-        <v>100</v>
-      </c>
-      <c r="K16" s="3">
-        <v>10</v>
-      </c>
-      <c r="L16" s="3">
-        <v>50</v>
-      </c>
-      <c r="M16" s="3">
-        <v>100</v>
-      </c>
-      <c r="N16" s="3">
-        <v>300</v>
-      </c>
-      <c r="O16" s="3">
-        <v>1</v>
-      </c>
-      <c r="P16" s="3">
-        <v>3</v>
-      </c>
-      <c r="Q16" s="3">
-        <v>1</v>
-      </c>
-      <c r="R16" s="3">
-        <v>2</v>
-      </c>
-      <c r="S16" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="T16" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="U16" s="3">
-        <v>0.03</v>
-      </c>
-      <c r="V16" s="3">
-        <v>0.04</v>
-      </c>
-      <c r="W16" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="X16" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="Y16" s="3">
-        <v>0.06</v>
-      </c>
-      <c r="Z16" s="3">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="AA16" s="3">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="AB16" s="3">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="17" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="18" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="16" s="3" customFormat="1" customHeight="1"/>
+    <row r="17" s="3" customFormat="1" customHeight="1"/>
+    <row r="18" s="3" customFormat="1" customHeight="1"/>
+    <row r="19" s="3" customFormat="1" customHeight="1"/>
+    <row r="20" s="3" customFormat="1" customHeight="1"/>
+    <row r="21" s="3" customFormat="1" customHeight="1"/>
+    <row r="22" s="3" customFormat="1" customHeight="1"/>
+    <row r="23" s="3" customFormat="1" customHeight="1"/>
+    <row r="24" s="3" customFormat="1" customHeight="1"/>
+    <row r="25" s="3" customFormat="1" customHeight="1"/>
+    <row r="26" s="3" customFormat="1" customHeight="1"/>
+    <row r="27" s="3" customFormat="1" customHeight="1"/>
+    <row r="28" s="3" customFormat="1" customHeight="1"/>
+    <row r="29" s="3" customFormat="1" customHeight="1"/>
+    <row r="30" s="3" customFormat="1" customHeight="1"/>
+    <row r="31" s="3" customFormat="1" customHeight="1"/>
+    <row r="32" s="3" customFormat="1" customHeight="1"/>
+    <row r="33" s="3" customFormat="1" customHeight="1"/>
+    <row r="34" s="3" customFormat="1" customHeight="1"/>
+    <row r="35" s="3" customFormat="1" customHeight="1"/>
+    <row r="36" s="3" customFormat="1" customHeight="1"/>
+    <row r="37" s="3" customFormat="1" customHeight="1"/>
+    <row r="38" s="3" customFormat="1" customHeight="1"/>
+    <row r="39" s="3" customFormat="1" customHeight="1"/>
+    <row r="40" s="3" customFormat="1" customHeight="1"/>
+    <row r="41" s="3" customFormat="1" customHeight="1"/>
+    <row r="42" s="3" customFormat="1" customHeight="1"/>
+    <row r="43" s="3" customFormat="1" customHeight="1"/>
+    <row r="44" s="3" customFormat="1" customHeight="1"/>
+    <row r="45" s="3" customFormat="1" customHeight="1"/>
+    <row r="46" s="3" customFormat="1" customHeight="1"/>
+    <row r="47" s="3" customFormat="1" customHeight="1"/>
+    <row r="48" s="3" customFormat="1" customHeight="1"/>
+    <row r="49" s="3" customFormat="1" customHeight="1"/>
+    <row r="50" s="3" customFormat="1" customHeight="1"/>
+    <row r="51" s="3" customFormat="1" customHeight="1"/>
+    <row r="52" s="3" customFormat="1" customHeight="1"/>
+    <row r="53" s="3" customFormat="1" customHeight="1"/>
+    <row r="54" s="3" customFormat="1" customHeight="1"/>
+    <row r="55" s="3" customFormat="1" customHeight="1"/>
+    <row r="56" s="3" customFormat="1" customHeight="1"/>
+    <row r="57" s="3" customFormat="1" customHeight="1"/>
+    <row r="58" s="3" customFormat="1" customHeight="1"/>
+    <row r="59" s="3" customFormat="1" customHeight="1"/>
+    <row r="60" s="3" customFormat="1" customHeight="1"/>
+    <row r="61" s="3" customFormat="1" customHeight="1"/>
+    <row r="62" s="3" customFormat="1" customHeight="1"/>
+    <row r="63" s="3" customFormat="1" customHeight="1"/>
+    <row r="64" s="3" customFormat="1" customHeight="1"/>
+    <row r="65" s="3" customFormat="1" customHeight="1"/>
+    <row r="66" s="3" customFormat="1" customHeight="1"/>
+    <row r="67" s="3" customFormat="1" customHeight="1"/>
+    <row r="68" s="3" customFormat="1" customHeight="1"/>
+    <row r="69" s="3" customFormat="1" customHeight="1"/>
+    <row r="70" s="3" customFormat="1" customHeight="1"/>
+    <row r="71" s="3" customFormat="1" customHeight="1"/>
+    <row r="72" s="3" customFormat="1" customHeight="1"/>
+    <row r="73" s="3" customFormat="1" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Unity/Assets/Config/Excel/EquipConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EquipConfig.xlsx
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="63">
   <si>
     <t>Id</t>
   </si>
@@ -278,25 +278,13 @@
     <t>一个衣服</t>
   </si>
   <si>
-    <t>一个腰带</t>
-  </si>
-  <si>
     <t>一个裤子</t>
   </si>
   <si>
     <t>一个鞋子</t>
   </si>
   <si>
-    <t>一个戒指</t>
-  </si>
-  <si>
-    <t>一个手镯</t>
-  </si>
-  <si>
     <t>一个项链</t>
-  </si>
-  <si>
-    <t>一个饰品</t>
   </si>
   <si>
     <t>一个武器</t>
@@ -1342,7 +1330,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:AB73"/>
+  <dimension ref="A3:AB69"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="10.875" style="4" customWidth="1"/>
@@ -2075,326 +2063,10 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="12" s="3" customFormat="1" customHeight="1" spans="3:28">
-      <c r="C12" s="3">
-        <v>12000007</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="I12" s="3">
-        <v>20</v>
-      </c>
-      <c r="J12" s="3">
-        <v>100</v>
-      </c>
-      <c r="K12" s="3">
-        <v>10</v>
-      </c>
-      <c r="L12" s="3">
-        <v>50</v>
-      </c>
-      <c r="M12" s="3">
-        <v>100</v>
-      </c>
-      <c r="N12" s="3">
-        <v>300</v>
-      </c>
-      <c r="O12" s="3">
-        <v>1</v>
-      </c>
-      <c r="P12" s="3">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>1</v>
-      </c>
-      <c r="R12" s="3">
-        <v>2</v>
-      </c>
-      <c r="S12" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="T12" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="U12" s="3">
-        <v>0.03</v>
-      </c>
-      <c r="V12" s="3">
-        <v>0.04</v>
-      </c>
-      <c r="W12" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="X12" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>0.06</v>
-      </c>
-      <c r="Z12" s="3">
-        <v>0.07</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>0.07</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="13" s="3" customFormat="1" customHeight="1" spans="3:28">
-      <c r="C13" s="3">
-        <v>12000008</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="I13" s="3">
-        <v>20</v>
-      </c>
-      <c r="J13" s="3">
-        <v>100</v>
-      </c>
-      <c r="K13" s="3">
-        <v>10</v>
-      </c>
-      <c r="L13" s="3">
-        <v>50</v>
-      </c>
-      <c r="M13" s="3">
-        <v>100</v>
-      </c>
-      <c r="N13" s="3">
-        <v>300</v>
-      </c>
-      <c r="O13" s="3">
-        <v>1</v>
-      </c>
-      <c r="P13" s="3">
-        <v>3</v>
-      </c>
-      <c r="Q13" s="3">
-        <v>1</v>
-      </c>
-      <c r="R13" s="3">
-        <v>2</v>
-      </c>
-      <c r="S13" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="T13" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="U13" s="3">
-        <v>0.03</v>
-      </c>
-      <c r="V13" s="3">
-        <v>0.04</v>
-      </c>
-      <c r="W13" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="X13" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="Y13" s="3">
-        <v>0.06</v>
-      </c>
-      <c r="Z13" s="3">
-        <v>0.07</v>
-      </c>
-      <c r="AA13" s="3">
-        <v>0.07</v>
-      </c>
-      <c r="AB13" s="3">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="14" s="3" customFormat="1" customHeight="1" spans="3:28">
-      <c r="C14" s="3">
-        <v>12000009</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="I14" s="3">
-        <v>20</v>
-      </c>
-      <c r="J14" s="3">
-        <v>100</v>
-      </c>
-      <c r="K14" s="3">
-        <v>10</v>
-      </c>
-      <c r="L14" s="3">
-        <v>50</v>
-      </c>
-      <c r="M14" s="3">
-        <v>100</v>
-      </c>
-      <c r="N14" s="3">
-        <v>300</v>
-      </c>
-      <c r="O14" s="3">
-        <v>1</v>
-      </c>
-      <c r="P14" s="3">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>1</v>
-      </c>
-      <c r="R14" s="3">
-        <v>2</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0.03</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0.04</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0.06</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0.07</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0.07</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="15" s="3" customFormat="1" customHeight="1" spans="3:28">
-      <c r="C15" s="3">
-        <v>12000010</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="I15" s="3">
-        <v>20</v>
-      </c>
-      <c r="J15" s="3">
-        <v>100</v>
-      </c>
-      <c r="K15" s="3">
-        <v>10</v>
-      </c>
-      <c r="L15" s="3">
-        <v>50</v>
-      </c>
-      <c r="M15" s="3">
-        <v>100</v>
-      </c>
-      <c r="N15" s="3">
-        <v>300</v>
-      </c>
-      <c r="O15" s="3">
-        <v>1</v>
-      </c>
-      <c r="P15" s="3">
-        <v>3</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>1</v>
-      </c>
-      <c r="R15" s="3">
-        <v>2</v>
-      </c>
-      <c r="S15" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="T15" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="U15" s="3">
-        <v>0.03</v>
-      </c>
-      <c r="V15" s="3">
-        <v>0.04</v>
-      </c>
-      <c r="W15" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="X15" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>0.06</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>0.07</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>0.07</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>0.08</v>
-      </c>
-    </row>
+    <row r="12" s="3" customFormat="1" customHeight="1"/>
+    <row r="13" s="3" customFormat="1" customHeight="1"/>
+    <row r="14" s="3" customFormat="1" customHeight="1"/>
+    <row r="15" s="3" customFormat="1" customHeight="1"/>
     <row r="16" s="3" customFormat="1" customHeight="1"/>
     <row r="17" s="3" customFormat="1" customHeight="1"/>
     <row r="18" s="3" customFormat="1" customHeight="1"/>
@@ -2449,10 +2121,6 @@
     <row r="67" s="3" customFormat="1" customHeight="1"/>
     <row r="68" s="3" customFormat="1" customHeight="1"/>
     <row r="69" s="3" customFormat="1" customHeight="1"/>
-    <row r="70" s="3" customFormat="1" customHeight="1"/>
-    <row r="71" s="3" customFormat="1" customHeight="1"/>
-    <row r="72" s="3" customFormat="1" customHeight="1"/>
-    <row r="73" s="3" customFormat="1" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/Unity/Assets/Config/Excel/EquipConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EquipConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="E3" authorId="0">
+    <comment ref="D3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -63,7 +63,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -99,11 +99,107 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="66">
+  <si>
+    <t>##var</t>
+  </si>
   <si>
     <t>Id</t>
   </si>
   <si>
+    <t>ItemName</t>
+  </si>
+  <si>
+    <t>HideType</t>
+  </si>
+  <si>
+    <t>HideShowPro</t>
+  </si>
+  <si>
+    <t>SellResourcesType</t>
+  </si>
+  <si>
+    <t>SellResourcesValue</t>
+  </si>
+  <si>
+    <t>Equip_MinAct</t>
+  </si>
+  <si>
+    <t>Equip_MaxAct</t>
+  </si>
+  <si>
+    <t>Equip_MinDef</t>
+  </si>
+  <si>
+    <t>Equip_MaxAdf</t>
+  </si>
+  <si>
+    <t>Equip_MinHp</t>
+  </si>
+  <si>
+    <t>Equip_MaxHp</t>
+  </si>
+  <si>
+    <t>Equip_MinAtkSpeed</t>
+  </si>
+  <si>
+    <t>Equip_MaxAtkSpeed</t>
+  </si>
+  <si>
+    <t>Equip_MinMoveSpeed</t>
+  </si>
+  <si>
+    <t>Equip_MaxMoveSpeed</t>
+  </si>
+  <si>
+    <t>Equip_Cri</t>
+  </si>
+  <si>
+    <t>Equip_Combo</t>
+  </si>
+  <si>
+    <t>Equip_Counterattack</t>
+  </si>
+  <si>
+    <t>Equip_LifeSteal</t>
+  </si>
+  <si>
+    <t>Equip_Eva</t>
+  </si>
+  <si>
+    <t>Equip_ReCri</t>
+  </si>
+  <si>
+    <t>Equip_ReCombo</t>
+  </si>
+  <si>
+    <t>Equip_ReCounterattack</t>
+  </si>
+  <si>
+    <t>Equip_ReLifeSteal</t>
+  </si>
+  <si>
+    <t>Equip_ReEva</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>(list#sep=,),int</t>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
     <t>装备名称</t>
   </si>
   <si>
@@ -174,93 +270,6 @@
   </si>
   <si>
     <t>抗闪避</t>
-  </si>
-  <si>
-    <t>ItemName</t>
-  </si>
-  <si>
-    <t>HideType</t>
-  </si>
-  <si>
-    <t>HideShowPro</t>
-  </si>
-  <si>
-    <t>SellResourcesType</t>
-  </si>
-  <si>
-    <t>SellResourcesValue</t>
-  </si>
-  <si>
-    <t>Equip_MinAct</t>
-  </si>
-  <si>
-    <t>Equip_MaxAct</t>
-  </si>
-  <si>
-    <t>Equip_MinDef</t>
-  </si>
-  <si>
-    <t>Equip_MaxAdf</t>
-  </si>
-  <si>
-    <t>Equip_MinHp</t>
-  </si>
-  <si>
-    <t>Equip_MaxHp</t>
-  </si>
-  <si>
-    <t>Equip_MinAtkSpeed</t>
-  </si>
-  <si>
-    <t>Equip_MaxAtkSpeed</t>
-  </si>
-  <si>
-    <t>Equip_MinMoveSpeed</t>
-  </si>
-  <si>
-    <t>Equip_MaxMoveSpeed</t>
-  </si>
-  <si>
-    <t>Equip_Cri</t>
-  </si>
-  <si>
-    <t>Equip_Combo</t>
-  </si>
-  <si>
-    <t>Equip_Counterattack</t>
-  </si>
-  <si>
-    <t>Equip_LifeSteal</t>
-  </si>
-  <si>
-    <t>Equip_Eva</t>
-  </si>
-  <si>
-    <t>Equip_ReCri</t>
-  </si>
-  <si>
-    <t>Equip_ReCombo</t>
-  </si>
-  <si>
-    <t>Equip_ReCounterattack</t>
-  </si>
-  <si>
-    <t>Equip_ReLifeSteal</t>
-  </si>
-  <si>
-    <t>Equip_ReEva</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>int[]</t>
-  </si>
-  <si>
-    <t>double</t>
   </si>
   <si>
     <t>一个头盔</t>
@@ -490,13 +499,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="1" tint="0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.749992370372631"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -986,29 +995,23 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1330,797 +1333,800 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:AB69"/>
+  <dimension ref="A1:AA67"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="10.875" style="4" customWidth="1"/>
-    <col min="3" max="16384" width="17.875" style="4"/>
+    <col min="1" max="1" width="10.875" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="17.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:28">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
+    <row r="1" customHeight="1" spans="1:27">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="1:27">
+      <c r="A2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:27">
+      <c r="A3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="C3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="U3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="V3" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="W3" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="X3" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z3" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA3" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" customHeight="1" spans="2:27">
+      <c r="B4" s="2">
+        <v>12000001</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4" s="2">
+        <v>20</v>
+      </c>
+      <c r="I4" s="2">
+        <v>100</v>
+      </c>
+      <c r="J4" s="2">
+        <v>10</v>
+      </c>
+      <c r="K4" s="2">
+        <v>50</v>
+      </c>
+      <c r="L4" s="2">
+        <v>100</v>
+      </c>
+      <c r="M4" s="2">
+        <v>300</v>
+      </c>
+      <c r="N4" s="2">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="O4" s="2">
+        <v>3</v>
+      </c>
+      <c r="P4" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="2">
         <v>2</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="R4" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="S4" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="T4" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="U4" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="V4" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="W4" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="X4" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="Y4" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="Z4" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="AA4" s="2">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="5" s="2" customFormat="1" customHeight="1" spans="2:27">
+      <c r="B5" s="2">
+        <v>12000002</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" s="2">
+        <v>20</v>
+      </c>
+      <c r="I5" s="2">
+        <v>100</v>
+      </c>
+      <c r="J5" s="2">
+        <v>10</v>
+      </c>
+      <c r="K5" s="2">
+        <v>50</v>
+      </c>
+      <c r="L5" s="2">
+        <v>100</v>
+      </c>
+      <c r="M5" s="2">
+        <v>300</v>
+      </c>
+      <c r="N5" s="2">
+        <v>1</v>
+      </c>
+      <c r="O5" s="2">
         <v>3</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="M3" s="6" t="s">
+      <c r="P5" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>2</v>
+      </c>
+      <c r="R5" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="S5" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="T5" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="U5" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="V5" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="W5" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="X5" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="Y5" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="Z5" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="AA5" s="2">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="2:27">
+      <c r="B6" s="2">
+        <v>12000003</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H6" s="2">
+        <v>20</v>
+      </c>
+      <c r="I6" s="2">
+        <v>100</v>
+      </c>
+      <c r="J6" s="2">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="S3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="T3" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="U3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="V3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="W3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="X3" s="6" t="s">
+      <c r="K6" s="2">
+        <v>50</v>
+      </c>
+      <c r="L6" s="2">
+        <v>100</v>
+      </c>
+      <c r="M6" s="2">
+        <v>300</v>
+      </c>
+      <c r="N6" s="2">
+        <v>1</v>
+      </c>
+      <c r="O6" s="2">
+        <v>3</v>
+      </c>
+      <c r="P6" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>2</v>
+      </c>
+      <c r="R6" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="S6" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="T6" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="U6" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="V6" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="W6" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="X6" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="Y6" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="AA6" s="2">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="2:27">
+      <c r="B7" s="2">
+        <v>12000004</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H7" s="2">
         <v>20</v>
       </c>
-      <c r="Y3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA3" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB3" s="6" t="s">
-        <v>24</v>
+      <c r="I7" s="2">
+        <v>100</v>
+      </c>
+      <c r="J7" s="2">
+        <v>10</v>
+      </c>
+      <c r="K7" s="2">
+        <v>50</v>
+      </c>
+      <c r="L7" s="2">
+        <v>100</v>
+      </c>
+      <c r="M7" s="2">
+        <v>300</v>
+      </c>
+      <c r="N7" s="2">
+        <v>1</v>
+      </c>
+      <c r="O7" s="2">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>2</v>
+      </c>
+      <c r="R7" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="S7" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="T7" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="U7" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="V7" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="W7" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="X7" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="Y7" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="Z7" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>0.08</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:28">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="P4" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q4" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="R4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="S4" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="T4" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="U4" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="V4" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="W4" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="X4" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y4" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z4" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA4" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB4" s="7" t="s">
-        <v>49</v>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="2:27">
+      <c r="B8" s="2">
+        <v>12000005</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H8" s="2">
+        <v>20</v>
+      </c>
+      <c r="I8" s="2">
+        <v>100</v>
+      </c>
+      <c r="J8" s="2">
+        <v>10</v>
+      </c>
+      <c r="K8" s="2">
+        <v>50</v>
+      </c>
+      <c r="L8" s="2">
+        <v>100</v>
+      </c>
+      <c r="M8" s="2">
+        <v>300</v>
+      </c>
+      <c r="N8" s="2">
+        <v>1</v>
+      </c>
+      <c r="O8" s="2">
+        <v>3</v>
+      </c>
+      <c r="P8" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>2</v>
+      </c>
+      <c r="R8" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="S8" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="T8" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="U8" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="V8" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="W8" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="X8" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="Y8" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="Z8" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="AA8" s="2">
+        <v>0.08</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" customHeight="1" spans="1:28">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="5" t="s">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:27">
+      <c r="B9" s="2">
+        <v>12000006</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" s="2">
+        <v>20</v>
+      </c>
+      <c r="I9" s="2">
+        <v>100</v>
+      </c>
+      <c r="J9" s="2">
+        <v>10</v>
+      </c>
+      <c r="K9" s="2">
         <v>50</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q5" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="R5" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="S5" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="T5" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="U5" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="V5" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="W5" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="X5" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y5" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z5" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AA5" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB5" s="5" t="s">
-        <v>53</v>
+      <c r="L9" s="2">
+        <v>100</v>
+      </c>
+      <c r="M9" s="2">
+        <v>300</v>
+      </c>
+      <c r="N9" s="2">
+        <v>1</v>
+      </c>
+      <c r="O9" s="2">
+        <v>3</v>
+      </c>
+      <c r="P9" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>2</v>
+      </c>
+      <c r="R9" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="S9" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="T9" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="U9" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="V9" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="W9" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="X9" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="Y9" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="Z9" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>0.08</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" customHeight="1" spans="3:28">
-      <c r="C6" s="3">
-        <v>12000001</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="I6" s="3">
-        <v>20</v>
-      </c>
-      <c r="J6" s="3">
-        <v>100</v>
-      </c>
-      <c r="K6" s="3">
-        <v>10</v>
-      </c>
-      <c r="L6" s="3">
-        <v>50</v>
-      </c>
-      <c r="M6" s="3">
-        <v>100</v>
-      </c>
-      <c r="N6" s="3">
-        <v>300</v>
-      </c>
-      <c r="O6" s="3">
-        <v>1</v>
-      </c>
-      <c r="P6" s="3">
-        <v>3</v>
-      </c>
-      <c r="Q6" s="3">
-        <v>1</v>
-      </c>
-      <c r="R6" s="3">
-        <v>2</v>
-      </c>
-      <c r="S6" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="T6" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="U6" s="3">
-        <v>0.03</v>
-      </c>
-      <c r="V6" s="3">
-        <v>0.04</v>
-      </c>
-      <c r="W6" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="X6" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="Y6" s="3">
-        <v>0.06</v>
-      </c>
-      <c r="Z6" s="3">
-        <v>0.07</v>
-      </c>
-      <c r="AA6" s="3">
-        <v>0.07</v>
-      </c>
-      <c r="AB6" s="3">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="7" s="3" customFormat="1" customHeight="1" spans="3:28">
-      <c r="C7" s="3">
-        <v>12000002</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="I7" s="3">
-        <v>20</v>
-      </c>
-      <c r="J7" s="3">
-        <v>100</v>
-      </c>
-      <c r="K7" s="3">
-        <v>10</v>
-      </c>
-      <c r="L7" s="3">
-        <v>50</v>
-      </c>
-      <c r="M7" s="3">
-        <v>100</v>
-      </c>
-      <c r="N7" s="3">
-        <v>300</v>
-      </c>
-      <c r="O7" s="3">
-        <v>1</v>
-      </c>
-      <c r="P7" s="3">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="3">
-        <v>1</v>
-      </c>
-      <c r="R7" s="3">
-        <v>2</v>
-      </c>
-      <c r="S7" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="T7" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="U7" s="3">
-        <v>0.03</v>
-      </c>
-      <c r="V7" s="3">
-        <v>0.04</v>
-      </c>
-      <c r="W7" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="X7" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="Y7" s="3">
-        <v>0.06</v>
-      </c>
-      <c r="Z7" s="3">
-        <v>0.07</v>
-      </c>
-      <c r="AA7" s="3">
-        <v>0.07</v>
-      </c>
-      <c r="AB7" s="3">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="8" s="3" customFormat="1" customHeight="1" spans="3:28">
-      <c r="C8" s="3">
-        <v>12000003</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="I8" s="3">
-        <v>20</v>
-      </c>
-      <c r="J8" s="3">
-        <v>100</v>
-      </c>
-      <c r="K8" s="3">
-        <v>10</v>
-      </c>
-      <c r="L8" s="3">
-        <v>50</v>
-      </c>
-      <c r="M8" s="3">
-        <v>100</v>
-      </c>
-      <c r="N8" s="3">
-        <v>300</v>
-      </c>
-      <c r="O8" s="3">
-        <v>1</v>
-      </c>
-      <c r="P8" s="3">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>1</v>
-      </c>
-      <c r="R8" s="3">
-        <v>2</v>
-      </c>
-      <c r="S8" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="T8" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="U8" s="3">
-        <v>0.03</v>
-      </c>
-      <c r="V8" s="3">
-        <v>0.04</v>
-      </c>
-      <c r="W8" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="X8" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>0.06</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>0.07</v>
-      </c>
-      <c r="AA8" s="3">
-        <v>0.07</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="9" s="3" customFormat="1" customHeight="1" spans="3:28">
-      <c r="C9" s="3">
-        <v>12000004</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="I9" s="3">
-        <v>20</v>
-      </c>
-      <c r="J9" s="3">
-        <v>100</v>
-      </c>
-      <c r="K9" s="3">
-        <v>10</v>
-      </c>
-      <c r="L9" s="3">
-        <v>50</v>
-      </c>
-      <c r="M9" s="3">
-        <v>100</v>
-      </c>
-      <c r="N9" s="3">
-        <v>300</v>
-      </c>
-      <c r="O9" s="3">
-        <v>1</v>
-      </c>
-      <c r="P9" s="3">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>1</v>
-      </c>
-      <c r="R9" s="3">
-        <v>2</v>
-      </c>
-      <c r="S9" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="T9" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="U9" s="3">
-        <v>0.03</v>
-      </c>
-      <c r="V9" s="3">
-        <v>0.04</v>
-      </c>
-      <c r="W9" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="X9" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>0.06</v>
-      </c>
-      <c r="Z9" s="3">
-        <v>0.07</v>
-      </c>
-      <c r="AA9" s="3">
-        <v>0.07</v>
-      </c>
-      <c r="AB9" s="3">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="10" s="3" customFormat="1" customHeight="1" spans="3:28">
-      <c r="C10" s="3">
-        <v>12000005</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="I10" s="3">
-        <v>20</v>
-      </c>
-      <c r="J10" s="3">
-        <v>100</v>
-      </c>
-      <c r="K10" s="3">
-        <v>10</v>
-      </c>
-      <c r="L10" s="3">
-        <v>50</v>
-      </c>
-      <c r="M10" s="3">
-        <v>100</v>
-      </c>
-      <c r="N10" s="3">
-        <v>300</v>
-      </c>
-      <c r="O10" s="3">
-        <v>1</v>
-      </c>
-      <c r="P10" s="3">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>1</v>
-      </c>
-      <c r="R10" s="3">
-        <v>2</v>
-      </c>
-      <c r="S10" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="T10" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="U10" s="3">
-        <v>0.03</v>
-      </c>
-      <c r="V10" s="3">
-        <v>0.04</v>
-      </c>
-      <c r="W10" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="X10" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>0.06</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>0.07</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>0.07</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="11" s="3" customFormat="1" customHeight="1" spans="3:28">
-      <c r="C11" s="3">
-        <v>12000006</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="I11" s="3">
-        <v>20</v>
-      </c>
-      <c r="J11" s="3">
-        <v>100</v>
-      </c>
-      <c r="K11" s="3">
-        <v>10</v>
-      </c>
-      <c r="L11" s="3">
-        <v>50</v>
-      </c>
-      <c r="M11" s="3">
-        <v>100</v>
-      </c>
-      <c r="N11" s="3">
-        <v>300</v>
-      </c>
-      <c r="O11" s="3">
-        <v>1</v>
-      </c>
-      <c r="P11" s="3">
-        <v>3</v>
-      </c>
-      <c r="Q11" s="3">
-        <v>1</v>
-      </c>
-      <c r="R11" s="3">
-        <v>2</v>
-      </c>
-      <c r="S11" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="T11" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="U11" s="3">
-        <v>0.03</v>
-      </c>
-      <c r="V11" s="3">
-        <v>0.04</v>
-      </c>
-      <c r="W11" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="X11" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="Y11" s="3">
-        <v>0.06</v>
-      </c>
-      <c r="Z11" s="3">
-        <v>0.07</v>
-      </c>
-      <c r="AA11" s="3">
-        <v>0.07</v>
-      </c>
-      <c r="AB11" s="3">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="12" s="3" customFormat="1" customHeight="1"/>
-    <row r="13" s="3" customFormat="1" customHeight="1"/>
-    <row r="14" s="3" customFormat="1" customHeight="1"/>
-    <row r="15" s="3" customFormat="1" customHeight="1"/>
-    <row r="16" s="3" customFormat="1" customHeight="1"/>
-    <row r="17" s="3" customFormat="1" customHeight="1"/>
-    <row r="18" s="3" customFormat="1" customHeight="1"/>
-    <row r="19" s="3" customFormat="1" customHeight="1"/>
-    <row r="20" s="3" customFormat="1" customHeight="1"/>
-    <row r="21" s="3" customFormat="1" customHeight="1"/>
-    <row r="22" s="3" customFormat="1" customHeight="1"/>
-    <row r="23" s="3" customFormat="1" customHeight="1"/>
-    <row r="24" s="3" customFormat="1" customHeight="1"/>
-    <row r="25" s="3" customFormat="1" customHeight="1"/>
-    <row r="26" s="3" customFormat="1" customHeight="1"/>
-    <row r="27" s="3" customFormat="1" customHeight="1"/>
-    <row r="28" s="3" customFormat="1" customHeight="1"/>
-    <row r="29" s="3" customFormat="1" customHeight="1"/>
-    <row r="30" s="3" customFormat="1" customHeight="1"/>
-    <row r="31" s="3" customFormat="1" customHeight="1"/>
-    <row r="32" s="3" customFormat="1" customHeight="1"/>
-    <row r="33" s="3" customFormat="1" customHeight="1"/>
-    <row r="34" s="3" customFormat="1" customHeight="1"/>
-    <row r="35" s="3" customFormat="1" customHeight="1"/>
-    <row r="36" s="3" customFormat="1" customHeight="1"/>
-    <row r="37" s="3" customFormat="1" customHeight="1"/>
-    <row r="38" s="3" customFormat="1" customHeight="1"/>
-    <row r="39" s="3" customFormat="1" customHeight="1"/>
-    <row r="40" s="3" customFormat="1" customHeight="1"/>
-    <row r="41" s="3" customFormat="1" customHeight="1"/>
-    <row r="42" s="3" customFormat="1" customHeight="1"/>
-    <row r="43" s="3" customFormat="1" customHeight="1"/>
-    <row r="44" s="3" customFormat="1" customHeight="1"/>
-    <row r="45" s="3" customFormat="1" customHeight="1"/>
-    <row r="46" s="3" customFormat="1" customHeight="1"/>
-    <row r="47" s="3" customFormat="1" customHeight="1"/>
-    <row r="48" s="3" customFormat="1" customHeight="1"/>
-    <row r="49" s="3" customFormat="1" customHeight="1"/>
-    <row r="50" s="3" customFormat="1" customHeight="1"/>
-    <row r="51" s="3" customFormat="1" customHeight="1"/>
-    <row r="52" s="3" customFormat="1" customHeight="1"/>
-    <row r="53" s="3" customFormat="1" customHeight="1"/>
-    <row r="54" s="3" customFormat="1" customHeight="1"/>
-    <row r="55" s="3" customFormat="1" customHeight="1"/>
-    <row r="56" s="3" customFormat="1" customHeight="1"/>
-    <row r="57" s="3" customFormat="1" customHeight="1"/>
-    <row r="58" s="3" customFormat="1" customHeight="1"/>
-    <row r="59" s="3" customFormat="1" customHeight="1"/>
-    <row r="60" s="3" customFormat="1" customHeight="1"/>
-    <row r="61" s="3" customFormat="1" customHeight="1"/>
-    <row r="62" s="3" customFormat="1" customHeight="1"/>
-    <row r="63" s="3" customFormat="1" customHeight="1"/>
-    <row r="64" s="3" customFormat="1" customHeight="1"/>
-    <row r="65" s="3" customFormat="1" customHeight="1"/>
-    <row r="66" s="3" customFormat="1" customHeight="1"/>
-    <row r="67" s="3" customFormat="1" customHeight="1"/>
-    <row r="68" s="3" customFormat="1" customHeight="1"/>
-    <row r="69" s="3" customFormat="1" customHeight="1"/>
+    <row r="10" s="2" customFormat="1" customHeight="1"/>
+    <row r="11" s="2" customFormat="1" customHeight="1"/>
+    <row r="12" s="2" customFormat="1" customHeight="1"/>
+    <row r="13" s="2" customFormat="1" customHeight="1"/>
+    <row r="14" s="2" customFormat="1" customHeight="1"/>
+    <row r="15" s="2" customFormat="1" customHeight="1"/>
+    <row r="16" s="2" customFormat="1" customHeight="1"/>
+    <row r="17" s="2" customFormat="1" customHeight="1"/>
+    <row r="18" s="2" customFormat="1" customHeight="1"/>
+    <row r="19" s="2" customFormat="1" customHeight="1"/>
+    <row r="20" s="2" customFormat="1" customHeight="1"/>
+    <row r="21" s="2" customFormat="1" customHeight="1"/>
+    <row r="22" s="2" customFormat="1" customHeight="1"/>
+    <row r="23" s="2" customFormat="1" customHeight="1"/>
+    <row r="24" s="2" customFormat="1" customHeight="1"/>
+    <row r="25" s="2" customFormat="1" customHeight="1"/>
+    <row r="26" s="2" customFormat="1" customHeight="1"/>
+    <row r="27" s="2" customFormat="1" customHeight="1"/>
+    <row r="28" s="2" customFormat="1" customHeight="1"/>
+    <row r="29" s="2" customFormat="1" customHeight="1"/>
+    <row r="30" s="2" customFormat="1" customHeight="1"/>
+    <row r="31" s="2" customFormat="1" customHeight="1"/>
+    <row r="32" s="2" customFormat="1" customHeight="1"/>
+    <row r="33" s="2" customFormat="1" customHeight="1"/>
+    <row r="34" s="2" customFormat="1" customHeight="1"/>
+    <row r="35" s="2" customFormat="1" customHeight="1"/>
+    <row r="36" s="2" customFormat="1" customHeight="1"/>
+    <row r="37" s="2" customFormat="1" customHeight="1"/>
+    <row r="38" s="2" customFormat="1" customHeight="1"/>
+    <row r="39" s="2" customFormat="1" customHeight="1"/>
+    <row r="40" s="2" customFormat="1" customHeight="1"/>
+    <row r="41" s="2" customFormat="1" customHeight="1"/>
+    <row r="42" s="2" customFormat="1" customHeight="1"/>
+    <row r="43" s="2" customFormat="1" customHeight="1"/>
+    <row r="44" s="2" customFormat="1" customHeight="1"/>
+    <row r="45" s="2" customFormat="1" customHeight="1"/>
+    <row r="46" s="2" customFormat="1" customHeight="1"/>
+    <row r="47" s="2" customFormat="1" customHeight="1"/>
+    <row r="48" s="2" customFormat="1" customHeight="1"/>
+    <row r="49" s="2" customFormat="1" customHeight="1"/>
+    <row r="50" s="2" customFormat="1" customHeight="1"/>
+    <row r="51" s="2" customFormat="1" customHeight="1"/>
+    <row r="52" s="2" customFormat="1" customHeight="1"/>
+    <row r="53" s="2" customFormat="1" customHeight="1"/>
+    <row r="54" s="2" customFormat="1" customHeight="1"/>
+    <row r="55" s="2" customFormat="1" customHeight="1"/>
+    <row r="56" s="2" customFormat="1" customHeight="1"/>
+    <row r="57" s="2" customFormat="1" customHeight="1"/>
+    <row r="58" s="2" customFormat="1" customHeight="1"/>
+    <row r="59" s="2" customFormat="1" customHeight="1"/>
+    <row r="60" s="2" customFormat="1" customHeight="1"/>
+    <row r="61" s="2" customFormat="1" customHeight="1"/>
+    <row r="62" s="2" customFormat="1" customHeight="1"/>
+    <row r="63" s="2" customFormat="1" customHeight="1"/>
+    <row r="64" s="2" customFormat="1" customHeight="1"/>
+    <row r="65" s="2" customFormat="1" customHeight="1"/>
+    <row r="66" s="2" customFormat="1" customHeight="1"/>
+    <row r="67" s="2" customFormat="1" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/Unity/Assets/Config/Excel/EquipConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EquipConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12795"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="68">
   <si>
     <t>##var</t>
   </si>
@@ -131,13 +131,16 @@
     <t>Equip_MinDef</t>
   </si>
   <si>
+    <t>Equip_MaxDef</t>
+  </si>
+  <si>
+    <t>Equip_MinAdf</t>
+  </si>
+  <si>
     <t>Equip_MaxAdf</t>
   </si>
   <si>
-    <t>Equip_MinHp</t>
-  </si>
-  <si>
-    <t>Equip_MaxHp</t>
+    <t>Equip_Hp</t>
   </si>
   <si>
     <t>Equip_MinAtkSpeed</t>
@@ -227,10 +230,13 @@
     <t>最高防御</t>
   </si>
   <si>
-    <t>最低生命</t>
-  </si>
-  <si>
-    <t>最高生命</t>
+    <t>最低魔防</t>
+  </si>
+  <si>
+    <t>最高魔防</t>
+  </si>
+  <si>
+    <t>生命</t>
   </si>
   <si>
     <t>最低攻速</t>
@@ -480,13 +486,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1333,14 +1339,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA67"/>
+  <dimension ref="A1:AB67"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="1" customWidth="1"/>
     <col min="2" max="16384" width="17.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:27">
+    <row r="1" customHeight="1" spans="1:28">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1422,191 +1428,200 @@
       <c r="AA1" s="4" t="s">
         <v>26</v>
       </c>
+      <c r="AB1" s="4" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" customHeight="1" spans="1:27">
+    <row r="2" customHeight="1" spans="1:28">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="I2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Y2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Z2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:27">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:28">
       <c r="A3" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="R3" s="5" t="s">
         <v>47</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U3" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="W3" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="X3" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Y3" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Z3" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AA3" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="AB3" s="5" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" customHeight="1" spans="2:27">
+    <row r="4" s="2" customFormat="1" customHeight="1" spans="2:28">
       <c r="B4" s="2">
         <v>12000001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E4" s="2">
         <v>0.02</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H4" s="2">
         <v>20</v>
@@ -1621,72 +1636,75 @@
         <v>50</v>
       </c>
       <c r="L4" s="2">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M4" s="2">
+        <v>50</v>
+      </c>
+      <c r="N4" s="2">
         <v>300</v>
       </c>
-      <c r="N4" s="2">
+      <c r="O4" s="2">
         <v>1</v>
       </c>
-      <c r="O4" s="2">
+      <c r="P4" s="2">
         <v>3</v>
       </c>
-      <c r="P4" s="2">
+      <c r="Q4" s="2">
         <v>1</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="R4" s="2">
         <v>2</v>
       </c>
-      <c r="R4" s="2">
+      <c r="S4" s="2">
         <v>0.01</v>
       </c>
-      <c r="S4" s="2">
+      <c r="T4" s="2">
         <v>0.02</v>
       </c>
-      <c r="T4" s="2">
+      <c r="U4" s="2">
         <v>0.03</v>
       </c>
-      <c r="U4" s="2">
+      <c r="V4" s="2">
         <v>0.04</v>
-      </c>
-      <c r="V4" s="2">
-        <v>0.05</v>
       </c>
       <c r="W4" s="2">
         <v>0.05</v>
       </c>
       <c r="X4" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="Y4" s="2">
         <v>0.06</v>
-      </c>
-      <c r="Y4" s="2">
-        <v>0.07</v>
       </c>
       <c r="Z4" s="2">
         <v>0.07</v>
       </c>
       <c r="AA4" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="AB4" s="2">
         <v>0.08</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" customHeight="1" spans="2:27">
+    <row r="5" s="2" customFormat="1" customHeight="1" spans="2:28">
       <c r="B5" s="2">
         <v>12000002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E5" s="2">
         <v>0.02</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H5" s="2">
         <v>20</v>
@@ -1701,72 +1719,75 @@
         <v>50</v>
       </c>
       <c r="L5" s="2">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M5" s="2">
+        <v>50</v>
+      </c>
+      <c r="N5" s="2">
         <v>300</v>
       </c>
-      <c r="N5" s="2">
+      <c r="O5" s="2">
         <v>1</v>
       </c>
-      <c r="O5" s="2">
+      <c r="P5" s="2">
         <v>3</v>
       </c>
-      <c r="P5" s="2">
+      <c r="Q5" s="2">
         <v>1</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="R5" s="2">
         <v>2</v>
       </c>
-      <c r="R5" s="2">
+      <c r="S5" s="2">
         <v>0.01</v>
       </c>
-      <c r="S5" s="2">
+      <c r="T5" s="2">
         <v>0.02</v>
       </c>
-      <c r="T5" s="2">
+      <c r="U5" s="2">
         <v>0.03</v>
       </c>
-      <c r="U5" s="2">
+      <c r="V5" s="2">
         <v>0.04</v>
-      </c>
-      <c r="V5" s="2">
-        <v>0.05</v>
       </c>
       <c r="W5" s="2">
         <v>0.05</v>
       </c>
       <c r="X5" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="Y5" s="2">
         <v>0.06</v>
-      </c>
-      <c r="Y5" s="2">
-        <v>0.07</v>
       </c>
       <c r="Z5" s="2">
         <v>0.07</v>
       </c>
       <c r="AA5" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="AB5" s="2">
         <v>0.08</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="2:27">
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="2:28">
       <c r="B6" s="2">
         <v>12000003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E6" s="2">
         <v>0.02</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H6" s="2">
         <v>20</v>
@@ -1781,72 +1802,75 @@
         <v>50</v>
       </c>
       <c r="L6" s="2">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M6" s="2">
+        <v>50</v>
+      </c>
+      <c r="N6" s="2">
         <v>300</v>
       </c>
-      <c r="N6" s="2">
+      <c r="O6" s="2">
         <v>1</v>
       </c>
-      <c r="O6" s="2">
+      <c r="P6" s="2">
         <v>3</v>
       </c>
-      <c r="P6" s="2">
+      <c r="Q6" s="2">
         <v>1</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="R6" s="2">
         <v>2</v>
       </c>
-      <c r="R6" s="2">
+      <c r="S6" s="2">
         <v>0.01</v>
       </c>
-      <c r="S6" s="2">
+      <c r="T6" s="2">
         <v>0.02</v>
       </c>
-      <c r="T6" s="2">
+      <c r="U6" s="2">
         <v>0.03</v>
       </c>
-      <c r="U6" s="2">
+      <c r="V6" s="2">
         <v>0.04</v>
-      </c>
-      <c r="V6" s="2">
-        <v>0.05</v>
       </c>
       <c r="W6" s="2">
         <v>0.05</v>
       </c>
       <c r="X6" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="Y6" s="2">
         <v>0.06</v>
-      </c>
-      <c r="Y6" s="2">
-        <v>0.07</v>
       </c>
       <c r="Z6" s="2">
         <v>0.07</v>
       </c>
       <c r="AA6" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="AB6" s="2">
         <v>0.08</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="2:27">
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="2:28">
       <c r="B7" s="2">
         <v>12000004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E7" s="2">
         <v>0.02</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H7" s="2">
         <v>20</v>
@@ -1861,72 +1885,75 @@
         <v>50</v>
       </c>
       <c r="L7" s="2">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M7" s="2">
+        <v>50</v>
+      </c>
+      <c r="N7" s="2">
         <v>300</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>1</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>3</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>1</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>2</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>0.01</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>0.02</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>0.03</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>0.04</v>
-      </c>
-      <c r="V7" s="2">
-        <v>0.05</v>
       </c>
       <c r="W7" s="2">
         <v>0.05</v>
       </c>
       <c r="X7" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="Y7" s="2">
         <v>0.06</v>
-      </c>
-      <c r="Y7" s="2">
-        <v>0.07</v>
       </c>
       <c r="Z7" s="2">
         <v>0.07</v>
       </c>
       <c r="AA7" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="AB7" s="2">
         <v>0.08</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="2:27">
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="2:28">
       <c r="B8" s="2">
         <v>12000005</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E8" s="2">
         <v>0.02</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H8" s="2">
         <v>20</v>
@@ -1941,72 +1968,75 @@
         <v>50</v>
       </c>
       <c r="L8" s="2">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M8" s="2">
+        <v>50</v>
+      </c>
+      <c r="N8" s="2">
         <v>300</v>
       </c>
-      <c r="N8" s="2">
+      <c r="O8" s="2">
         <v>1</v>
       </c>
-      <c r="O8" s="2">
+      <c r="P8" s="2">
         <v>3</v>
       </c>
-      <c r="P8" s="2">
+      <c r="Q8" s="2">
         <v>1</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="R8" s="2">
         <v>2</v>
       </c>
-      <c r="R8" s="2">
+      <c r="S8" s="2">
         <v>0.01</v>
       </c>
-      <c r="S8" s="2">
+      <c r="T8" s="2">
         <v>0.02</v>
       </c>
-      <c r="T8" s="2">
+      <c r="U8" s="2">
         <v>0.03</v>
       </c>
-      <c r="U8" s="2">
+      <c r="V8" s="2">
         <v>0.04</v>
-      </c>
-      <c r="V8" s="2">
-        <v>0.05</v>
       </c>
       <c r="W8" s="2">
         <v>0.05</v>
       </c>
       <c r="X8" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="Y8" s="2">
         <v>0.06</v>
-      </c>
-      <c r="Y8" s="2">
-        <v>0.07</v>
       </c>
       <c r="Z8" s="2">
         <v>0.07</v>
       </c>
       <c r="AA8" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="AB8" s="2">
         <v>0.08</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:27">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:28">
       <c r="B9" s="2">
         <v>12000006</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E9" s="2">
         <v>0.02</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H9" s="2">
         <v>20</v>
@@ -2021,51 +2051,54 @@
         <v>50</v>
       </c>
       <c r="L9" s="2">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M9" s="2">
+        <v>50</v>
+      </c>
+      <c r="N9" s="2">
         <v>300</v>
       </c>
-      <c r="N9" s="2">
+      <c r="O9" s="2">
         <v>1</v>
       </c>
-      <c r="O9" s="2">
+      <c r="P9" s="2">
         <v>3</v>
       </c>
-      <c r="P9" s="2">
+      <c r="Q9" s="2">
         <v>1</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="R9" s="2">
         <v>2</v>
       </c>
-      <c r="R9" s="2">
+      <c r="S9" s="2">
         <v>0.01</v>
       </c>
-      <c r="S9" s="2">
+      <c r="T9" s="2">
         <v>0.02</v>
       </c>
-      <c r="T9" s="2">
+      <c r="U9" s="2">
         <v>0.03</v>
       </c>
-      <c r="U9" s="2">
+      <c r="V9" s="2">
         <v>0.04</v>
-      </c>
-      <c r="V9" s="2">
-        <v>0.05</v>
       </c>
       <c r="W9" s="2">
         <v>0.05</v>
       </c>
       <c r="X9" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="Y9" s="2">
         <v>0.06</v>
-      </c>
-      <c r="Y9" s="2">
-        <v>0.07</v>
       </c>
       <c r="Z9" s="2">
         <v>0.07</v>
       </c>
       <c r="AA9" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="AB9" s="2">
         <v>0.08</v>
       </c>
     </row>

--- a/Unity/Assets/Config/Excel/EquipConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EquipConfig.xlsx
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="65">
   <si>
     <t>##var</t>
   </si>
@@ -143,16 +143,10 @@
     <t>Equip_Hp</t>
   </si>
   <si>
-    <t>Equip_MinAtkSpeed</t>
-  </si>
-  <si>
-    <t>Equip_MaxAtkSpeed</t>
-  </si>
-  <si>
-    <t>Equip_MinMoveSpeed</t>
-  </si>
-  <si>
-    <t>Equip_MaxMoveSpeed</t>
+    <t>Equip_AtkSpeed</t>
+  </si>
+  <si>
+    <t>Equip_MoveSpeed</t>
   </si>
   <si>
     <t>Equip_Cri</t>
@@ -239,13 +233,10 @@
     <t>生命</t>
   </si>
   <si>
-    <t>最低攻速</t>
-  </si>
-  <si>
-    <t>最高攻速</t>
-  </si>
-  <si>
-    <t>最低移速</t>
+    <t>攻速</t>
+  </si>
+  <si>
+    <t>移速</t>
   </si>
   <si>
     <t>暴击</t>
@@ -1339,14 +1330,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB67"/>
+  <dimension ref="A1:Z67"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.875" style="1" customWidth="1"/>
     <col min="2" max="16384" width="17.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:28">
+    <row r="1" customHeight="1" spans="1:26">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1425,203 +1416,185 @@
       <c r="Z1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="4" t="s">
+    </row>
+    <row r="2" customHeight="1" spans="1:26">
+      <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="2" customHeight="1" spans="1:28">
-      <c r="A2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="3" t="s">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:26">
+      <c r="A3" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="W2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:28">
-      <c r="A3" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="K3" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="L3" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="M3" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="N3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="O3" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="P3" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="Q3" s="5" t="s">
         <v>46</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>48</v>
       </c>
       <c r="R3" s="5" t="s">
         <v>47</v>
       </c>
       <c r="S3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="T3" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="T3" s="5" t="s">
+      <c r="U3" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="U3" s="5" t="s">
+      <c r="V3" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="V3" s="5" t="s">
+      <c r="W3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="5" t="s">
+      <c r="X3" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="X3" s="5" t="s">
+      <c r="Y3" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="Y3" s="5" t="s">
+      <c r="Z3" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="Z3" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA3" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="AB3" s="5" t="s">
-        <v>58</v>
-      </c>
     </row>
-    <row r="4" s="2" customFormat="1" customHeight="1" spans="2:28">
+    <row r="4" s="2" customFormat="1" customHeight="1" spans="2:26">
       <c r="B4" s="2">
         <v>12000001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E4" s="2">
         <v>0.02</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H4" s="2">
         <v>20</v>
@@ -1645,66 +1618,60 @@
         <v>300</v>
       </c>
       <c r="O4" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P4" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q4" s="2">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="R4" s="2">
-        <v>2</v>
+        <v>0.02</v>
       </c>
       <c r="S4" s="2">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="T4" s="2">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="U4" s="2">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="V4" s="2">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="W4" s="2">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="X4" s="2">
-        <v>0.05</v>
+        <v>0.07</v>
       </c>
       <c r="Y4" s="2">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
       <c r="Z4" s="2">
-        <v>0.07</v>
-      </c>
-      <c r="AA4" s="2">
-        <v>0.07</v>
-      </c>
-      <c r="AB4" s="2">
         <v>0.08</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" customHeight="1" spans="2:28">
+    <row r="5" s="2" customFormat="1" customHeight="1" spans="2:26">
       <c r="B5" s="2">
         <v>12000002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E5" s="2">
         <v>0.02</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H5" s="2">
         <v>20</v>
@@ -1728,66 +1695,60 @@
         <v>300</v>
       </c>
       <c r="O5" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P5" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q5" s="2">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="R5" s="2">
-        <v>2</v>
+        <v>0.02</v>
       </c>
       <c r="S5" s="2">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="T5" s="2">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="U5" s="2">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="V5" s="2">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="W5" s="2">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="X5" s="2">
-        <v>0.05</v>
+        <v>0.07</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.07</v>
-      </c>
-      <c r="AA5" s="2">
-        <v>0.07</v>
-      </c>
-      <c r="AB5" s="2">
         <v>0.08</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="2:28">
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="2:26">
       <c r="B6" s="2">
         <v>12000003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E6" s="2">
         <v>0.02</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H6" s="2">
         <v>20</v>
@@ -1811,66 +1772,60 @@
         <v>300</v>
       </c>
       <c r="O6" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P6" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="2">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="R6" s="2">
-        <v>2</v>
+        <v>0.02</v>
       </c>
       <c r="S6" s="2">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="T6" s="2">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="U6" s="2">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="V6" s="2">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="W6" s="2">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="X6" s="2">
-        <v>0.05</v>
+        <v>0.07</v>
       </c>
       <c r="Y6" s="2">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.07</v>
-      </c>
-      <c r="AA6" s="2">
-        <v>0.07</v>
-      </c>
-      <c r="AB6" s="2">
         <v>0.08</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="2:28">
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="2:26">
       <c r="B7" s="2">
         <v>12000004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E7" s="2">
         <v>0.02</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H7" s="2">
         <v>20</v>
@@ -1894,66 +1849,60 @@
         <v>300</v>
       </c>
       <c r="O7" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P7" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q7" s="2">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="R7" s="2">
-        <v>2</v>
+        <v>0.02</v>
       </c>
       <c r="S7" s="2">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="T7" s="2">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="U7" s="2">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="V7" s="2">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="W7" s="2">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="X7" s="2">
-        <v>0.05</v>
+        <v>0.07</v>
       </c>
       <c r="Y7" s="2">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
       <c r="Z7" s="2">
-        <v>0.07</v>
-      </c>
-      <c r="AA7" s="2">
-        <v>0.07</v>
-      </c>
-      <c r="AB7" s="2">
         <v>0.08</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="2:28">
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="2:26">
       <c r="B8" s="2">
         <v>12000005</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E8" s="2">
         <v>0.02</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H8" s="2">
         <v>20</v>
@@ -1977,66 +1926,60 @@
         <v>300</v>
       </c>
       <c r="O8" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P8" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="2">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="R8" s="2">
-        <v>2</v>
+        <v>0.02</v>
       </c>
       <c r="S8" s="2">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="T8" s="2">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="U8" s="2">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="V8" s="2">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="W8" s="2">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="X8" s="2">
-        <v>0.05</v>
+        <v>0.07</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.07</v>
-      </c>
-      <c r="AA8" s="2">
-        <v>0.07</v>
-      </c>
-      <c r="AB8" s="2">
         <v>0.08</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:28">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="2:26">
       <c r="B9" s="2">
         <v>12000006</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E9" s="2">
         <v>0.02</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H9" s="2">
         <v>20</v>
@@ -2060,45 +2003,39 @@
         <v>300</v>
       </c>
       <c r="O9" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P9" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q9" s="2">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="R9" s="2">
-        <v>2</v>
+        <v>0.02</v>
       </c>
       <c r="S9" s="2">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="T9" s="2">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="U9" s="2">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="V9" s="2">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="W9" s="2">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="X9" s="2">
-        <v>0.05</v>
+        <v>0.07</v>
       </c>
       <c r="Y9" s="2">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.07</v>
-      </c>
-      <c r="AA9" s="2">
-        <v>0.07</v>
-      </c>
-      <c r="AB9" s="2">
         <v>0.08</v>
       </c>
     </row>

--- a/Unity/Assets/Config/Excel/EquipConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EquipConfig.xlsx
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="66">
   <si>
     <t>##var</t>
   </si>
@@ -294,6 +294,9 @@
   </si>
   <si>
     <t>一个武器</t>
+  </si>
+  <si>
+    <t>一个更吊的头盔</t>
   </si>
 </sst>
 </file>
@@ -477,13 +480,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2039,7 +2042,83 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" customHeight="1"/>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="2:26">
+      <c r="B10" s="2">
+        <v>12000011</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="2">
+        <v>40</v>
+      </c>
+      <c r="I10" s="2">
+        <v>200</v>
+      </c>
+      <c r="J10" s="2">
+        <v>10</v>
+      </c>
+      <c r="K10" s="2">
+        <v>50</v>
+      </c>
+      <c r="L10" s="2">
+        <v>50</v>
+      </c>
+      <c r="M10" s="2">
+        <v>50</v>
+      </c>
+      <c r="N10" s="2">
+        <v>300</v>
+      </c>
+      <c r="O10" s="2">
+        <v>3</v>
+      </c>
+      <c r="P10" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="R10" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="S10" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="T10" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="U10" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="V10" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="W10" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="X10" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="Y10" s="2">
+        <v>0.07</v>
+      </c>
+      <c r="Z10" s="2">
+        <v>0.08</v>
+      </c>
+    </row>
     <row r="11" s="2" customFormat="1" customHeight="1"/>
     <row r="12" s="2" customFormat="1" customHeight="1"/>
     <row r="13" s="2" customFormat="1" customHeight="1"/>

--- a/Unity/Assets/Config/Excel/EquipConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EquipConfig.xlsx
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="67">
   <si>
     <t>##var</t>
   </si>
@@ -192,6 +192,9 @@
   </si>
   <si>
     <t>double</t>
+  </si>
+  <si>
+    <t>long</t>
   </si>
   <si>
     <t>##</t>
@@ -1464,120 +1467,120 @@
         <v>27</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Y2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Z2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:26">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U3" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="W3" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="X3" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Y3" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Z3" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1" customHeight="1" spans="2:26">
@@ -1585,19 +1588,19 @@
         <v>12000001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E4" s="2">
         <v>0.02</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H4" s="2">
         <v>20</v>
@@ -1621,40 +1624,40 @@
         <v>300</v>
       </c>
       <c r="O4" s="2">
-        <v>3</v>
+        <v>30000</v>
       </c>
       <c r="P4" s="2">
-        <v>2</v>
+        <v>20000</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.01</v>
+        <v>100</v>
       </c>
       <c r="R4" s="2">
-        <v>0.02</v>
+        <v>200</v>
       </c>
       <c r="S4" s="2">
-        <v>0.03</v>
+        <v>300</v>
       </c>
       <c r="T4" s="2">
-        <v>0.04</v>
+        <v>400</v>
       </c>
       <c r="U4" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="V4" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="W4" s="2">
-        <v>0.06</v>
+        <v>600</v>
       </c>
       <c r="X4" s="2">
-        <v>0.07</v>
+        <v>700</v>
       </c>
       <c r="Y4" s="2">
-        <v>0.07</v>
+        <v>700</v>
       </c>
       <c r="Z4" s="2">
-        <v>0.08</v>
+        <v>800</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" customHeight="1" spans="2:26">
@@ -1662,19 +1665,19 @@
         <v>12000002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E5" s="2">
         <v>0.02</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H5" s="2">
         <v>20</v>
@@ -1698,40 +1701,40 @@
         <v>300</v>
       </c>
       <c r="O5" s="2">
-        <v>3</v>
+        <v>30000</v>
       </c>
       <c r="P5" s="2">
-        <v>2</v>
+        <v>20000</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.01</v>
+        <v>100</v>
       </c>
       <c r="R5" s="2">
-        <v>0.02</v>
+        <v>200</v>
       </c>
       <c r="S5" s="2">
-        <v>0.03</v>
+        <v>300</v>
       </c>
       <c r="T5" s="2">
-        <v>0.04</v>
+        <v>400</v>
       </c>
       <c r="U5" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="V5" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="W5" s="2">
-        <v>0.06</v>
+        <v>600</v>
       </c>
       <c r="X5" s="2">
-        <v>0.07</v>
+        <v>700</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.07</v>
+        <v>700</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.08</v>
+        <v>800</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="2:26">
@@ -1739,19 +1742,19 @@
         <v>12000003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E6" s="2">
         <v>0.02</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H6" s="2">
         <v>20</v>
@@ -1775,40 +1778,40 @@
         <v>300</v>
       </c>
       <c r="O6" s="2">
-        <v>3</v>
+        <v>30000</v>
       </c>
       <c r="P6" s="2">
-        <v>2</v>
+        <v>20000</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.01</v>
+        <v>100</v>
       </c>
       <c r="R6" s="2">
-        <v>0.02</v>
+        <v>200</v>
       </c>
       <c r="S6" s="2">
-        <v>0.03</v>
+        <v>300</v>
       </c>
       <c r="T6" s="2">
-        <v>0.04</v>
+        <v>400</v>
       </c>
       <c r="U6" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="V6" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="W6" s="2">
-        <v>0.06</v>
+        <v>600</v>
       </c>
       <c r="X6" s="2">
-        <v>0.07</v>
+        <v>700</v>
       </c>
       <c r="Y6" s="2">
-        <v>0.07</v>
+        <v>700</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.08</v>
+        <v>800</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" customHeight="1" spans="2:26">
@@ -1816,19 +1819,19 @@
         <v>12000004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E7" s="2">
         <v>0.02</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H7" s="2">
         <v>20</v>
@@ -1852,40 +1855,40 @@
         <v>300</v>
       </c>
       <c r="O7" s="2">
-        <v>3</v>
+        <v>30000</v>
       </c>
       <c r="P7" s="2">
-        <v>2</v>
+        <v>20000</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.01</v>
+        <v>100</v>
       </c>
       <c r="R7" s="2">
-        <v>0.02</v>
+        <v>200</v>
       </c>
       <c r="S7" s="2">
-        <v>0.03</v>
+        <v>300</v>
       </c>
       <c r="T7" s="2">
-        <v>0.04</v>
+        <v>400</v>
       </c>
       <c r="U7" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="V7" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="W7" s="2">
-        <v>0.06</v>
+        <v>600</v>
       </c>
       <c r="X7" s="2">
-        <v>0.07</v>
+        <v>700</v>
       </c>
       <c r="Y7" s="2">
-        <v>0.07</v>
+        <v>700</v>
       </c>
       <c r="Z7" s="2">
-        <v>0.08</v>
+        <v>800</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="2:26">
@@ -1893,19 +1896,19 @@
         <v>12000005</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E8" s="2">
         <v>0.02</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H8" s="2">
         <v>20</v>
@@ -1929,40 +1932,40 @@
         <v>300</v>
       </c>
       <c r="O8" s="2">
-        <v>3</v>
+        <v>30000</v>
       </c>
       <c r="P8" s="2">
-        <v>2</v>
+        <v>20000</v>
       </c>
       <c r="Q8" s="2">
-        <v>0.01</v>
+        <v>100</v>
       </c>
       <c r="R8" s="2">
-        <v>0.02</v>
+        <v>200</v>
       </c>
       <c r="S8" s="2">
-        <v>0.03</v>
+        <v>300</v>
       </c>
       <c r="T8" s="2">
-        <v>0.04</v>
+        <v>400</v>
       </c>
       <c r="U8" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="V8" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="W8" s="2">
-        <v>0.06</v>
+        <v>600</v>
       </c>
       <c r="X8" s="2">
-        <v>0.07</v>
+        <v>700</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.07</v>
+        <v>700</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.08</v>
+        <v>800</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="2:26">
@@ -1970,19 +1973,19 @@
         <v>12000006</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E9" s="2">
         <v>0.02</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H9" s="2">
         <v>20</v>
@@ -2006,40 +2009,40 @@
         <v>300</v>
       </c>
       <c r="O9" s="2">
-        <v>3</v>
+        <v>30000</v>
       </c>
       <c r="P9" s="2">
-        <v>2</v>
+        <v>20000</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.01</v>
+        <v>100</v>
       </c>
       <c r="R9" s="2">
-        <v>0.02</v>
+        <v>200</v>
       </c>
       <c r="S9" s="2">
-        <v>0.03</v>
+        <v>300</v>
       </c>
       <c r="T9" s="2">
-        <v>0.04</v>
+        <v>400</v>
       </c>
       <c r="U9" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="V9" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="W9" s="2">
-        <v>0.06</v>
+        <v>600</v>
       </c>
       <c r="X9" s="2">
-        <v>0.07</v>
+        <v>700</v>
       </c>
       <c r="Y9" s="2">
-        <v>0.07</v>
+        <v>700</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.08</v>
+        <v>800</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="2:26">
@@ -2047,19 +2050,19 @@
         <v>12000011</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E10" s="2">
         <v>0.02</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H10" s="2">
         <v>40</v>
@@ -2083,40 +2086,40 @@
         <v>300</v>
       </c>
       <c r="O10" s="2">
-        <v>3</v>
+        <v>30000</v>
       </c>
       <c r="P10" s="2">
-        <v>2</v>
+        <v>20000</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.01</v>
+        <v>100</v>
       </c>
       <c r="R10" s="2">
-        <v>0.02</v>
+        <v>200</v>
       </c>
       <c r="S10" s="2">
-        <v>0.03</v>
+        <v>300</v>
       </c>
       <c r="T10" s="2">
-        <v>0.04</v>
+        <v>400</v>
       </c>
       <c r="U10" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="V10" s="2">
-        <v>0.05</v>
+        <v>500</v>
       </c>
       <c r="W10" s="2">
-        <v>0.06</v>
+        <v>600</v>
       </c>
       <c r="X10" s="2">
-        <v>0.07</v>
+        <v>700</v>
       </c>
       <c r="Y10" s="2">
-        <v>0.07</v>
+        <v>700</v>
       </c>
       <c r="Z10" s="2">
-        <v>0.08</v>
+        <v>800</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" customHeight="1"/>
